--- a/Agentic_Healthcare_Assistant/data_storage/runtime_records.xlsx
+++ b/Agentic_Healthcare_Assistant/data_storage/runtime_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,6 +635,33 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>33-year-old female presenting with 5-day history of dry cough, nasal congestion, and low-grade fever. Diagnosis: Acute Upper Respiratory Infection (ICD-10 J06.9). Plan: Symptomatic relief with hydration, antipyretics, and antihistamines; no antibiotics required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>+91-99999-88888</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Test Evaluation Patient</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Updated test summary after visit</t>
         </is>
       </c>
     </row>
